--- a/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB122"/>
+  <dimension ref="A1:AD122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,16 @@
       <c r="AB1" t="inlineStr">
         <is>
           <t>ubigeo</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ugel</t>
         </is>
       </c>
     </row>
@@ -651,6 +661,16 @@
           <t>020803</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -743,6 +763,16 @@
           <t>022003</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -837,6 +867,16 @@
           <t>021010</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -929,6 +969,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1021,6 +1071,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1113,6 +1173,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1205,6 +1275,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1297,6 +1377,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1389,6 +1479,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1487,6 +1587,16 @@
           <t>030603</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1583,6 +1693,16 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>030603</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
         </is>
       </c>
     </row>
@@ -1669,6 +1789,16 @@
           <t>030603</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1765,6 +1895,16 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>030603</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
         </is>
       </c>
     </row>
@@ -1851,6 +1991,16 @@
           <t>030603</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1947,6 +2097,16 @@
           <t>030603</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2047,6 +2207,16 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>030415</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>UGEL AYMARAES</t>
         </is>
       </c>
     </row>
@@ -2139,6 +2309,16 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>040104</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
     </row>
@@ -2227,6 +2407,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2313,6 +2503,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2399,6 +2599,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2485,6 +2695,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2571,6 +2791,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2663,6 +2893,16 @@
           <t>050102</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2755,6 +2995,16 @@
           <t>050102</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2847,6 +3097,16 @@
           <t>050102</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2939,6 +3199,16 @@
           <t>050103</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3031,6 +3301,16 @@
           <t>050510</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3123,6 +3403,16 @@
           <t>050510</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3215,6 +3505,16 @@
           <t>050510</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3307,6 +3607,16 @@
           <t>050510</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3399,6 +3709,16 @@
           <t>050510</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3493,6 +3813,16 @@
           <t>050116</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3585,6 +3915,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3677,6 +4017,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3769,6 +4119,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3861,6 +4221,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3953,6 +4323,16 @@
           <t>050104</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4045,6 +4425,16 @@
           <t>050104</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4147,6 +4537,16 @@
           <t>050504</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4249,6 +4649,16 @@
           <t>050504</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4351,6 +4761,16 @@
           <t>050504</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4453,6 +4873,16 @@
           <t>050504</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4553,6 +4983,16 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>050504</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
     </row>
@@ -4643,6 +5083,16 @@
           <t>051010</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4737,6 +5187,16 @@
           <t>051001</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4829,6 +5289,16 @@
           <t>050401</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4921,6 +5391,16 @@
           <t>050408</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5013,6 +5493,16 @@
           <t>050408</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5115,6 +5605,16 @@
           <t>050514</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5211,6 +5711,16 @@
           <t>050411</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5305,6 +5815,16 @@
           <t>050411</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5403,6 +5923,16 @@
           <t>050411</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5495,6 +6025,16 @@
           <t>050705</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5587,6 +6127,16 @@
           <t>050705</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5679,6 +6229,16 @@
           <t>050705</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5771,6 +6331,16 @@
           <t>050705</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5863,6 +6433,16 @@
           <t>050705</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5955,6 +6535,16 @@
           <t>050705</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6047,6 +6637,16 @@
           <t>050705</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6139,6 +6739,16 @@
           <t>050705</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6231,6 +6841,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6323,6 +6943,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6425,6 +7055,16 @@
           <t>051011</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6517,6 +7157,16 @@
           <t>050112</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6611,6 +7261,16 @@
           <t>050112</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6703,6 +7363,16 @@
           <t>050113</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6795,6 +7465,16 @@
           <t>050410</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6887,6 +7567,16 @@
           <t>050114</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6989,6 +7679,16 @@
           <t>061106</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7091,6 +7791,16 @@
           <t>061106</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7187,6 +7897,16 @@
       <c r="AB72" t="inlineStr">
         <is>
           <t>080803</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
         </is>
       </c>
     </row>
@@ -7271,6 +7991,16 @@
           <t>080911</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7353,6 +8083,16 @@
           <t>080911</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7435,6 +8175,16 @@
           <t>080911</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7517,6 +8267,16 @@
           <t>080911</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7611,6 +8371,16 @@
           <t>080805</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7705,6 +8475,16 @@
           <t>080805</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7793,6 +8573,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7881,6 +8671,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7969,6 +8769,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8057,6 +8867,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8143,6 +8963,16 @@
       <c r="AB83" t="inlineStr">
         <is>
           <t>080910</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
     </row>
@@ -8233,6 +9063,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8319,6 +9159,16 @@
       <c r="AB85" t="inlineStr">
         <is>
           <t>080910</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
     </row>
@@ -8403,6 +9253,16 @@
           <t>090307</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8513,6 +9373,16 @@
           <t>100101</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8607,6 +9477,16 @@
           <t>120603</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8705,6 +9585,16 @@
           <t>120603</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8801,6 +9691,16 @@
       <c r="AB90" t="inlineStr">
         <is>
           <t>120603</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
         </is>
       </c>
     </row>
@@ -8897,6 +9797,16 @@
           <t>130107</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8995,6 +9905,16 @@
       <c r="AB92" t="inlineStr">
         <is>
           <t>130107</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
     </row>
@@ -9087,6 +10007,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9175,6 +10105,16 @@
       <c r="AB94" t="inlineStr">
         <is>
           <t>150103</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
     </row>
@@ -9261,6 +10201,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9351,6 +10301,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9441,6 +10401,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9539,6 +10509,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -9637,6 +10617,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9735,6 +10725,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9831,6 +10831,16 @@
       <c r="AB101" t="inlineStr">
         <is>
           <t>150601</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
     </row>
@@ -9925,6 +10935,16 @@
           <t>150812</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10027,6 +11047,16 @@
           <t>160510</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10115,6 +11145,16 @@
           <t>160801</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>UGEL PUTUMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10203,6 +11243,16 @@
           <t>160801</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>UGEL PUTUMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10297,6 +11347,16 @@
           <t>200802</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10383,6 +11443,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -10485,6 +11555,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -10587,6 +11667,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10689,6 +11779,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -10791,6 +11891,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10891,6 +12001,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10993,6 +12113,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11095,6 +12225,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11197,6 +12337,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11299,6 +12449,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11393,6 +12553,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -11493,6 +12663,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -11603,6 +12783,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -11703,6 +12893,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -11805,6 +13005,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -11907,6 +13117,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD122"/>
+  <dimension ref="A1:AE122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,11 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>ugel</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -671,6 +676,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Comandante Noel</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -773,6 +783,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -877,6 +892,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Paucas</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -979,6 +999,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1081,6 +1106,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1183,6 +1213,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1285,6 +1320,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1387,6 +1427,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1489,6 +1534,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1597,6 +1647,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cocharcas</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1703,6 +1758,11 @@
       <c r="AD12" t="inlineStr">
         <is>
           <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cocharcas</t>
         </is>
       </c>
     </row>
@@ -1799,6 +1859,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cocharcas</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1905,6 +1970,11 @@
       <c r="AD14" t="inlineStr">
         <is>
           <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cocharcas</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2071,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cocharcas</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2107,6 +2182,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cocharcas</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2217,6 +2297,11 @@
       <c r="AD17" t="inlineStr">
         <is>
           <t>UGEL AYMARAES</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tintay</t>
         </is>
       </c>
     </row>
@@ -2319,6 +2404,11 @@
       <c r="AD18" t="inlineStr">
         <is>
           <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
     </row>
@@ -2417,6 +2507,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2513,6 +2608,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2609,6 +2709,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2705,6 +2810,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2801,6 +2911,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3209,6 +3339,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3311,6 +3446,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3413,6 +3553,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3515,6 +3660,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3617,6 +3767,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3719,6 +3874,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3823,6 +3983,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3925,6 +4090,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4027,6 +4197,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4129,6 +4304,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4231,6 +4411,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4333,6 +4518,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4435,6 +4625,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4547,6 +4742,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chilcas</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4659,6 +4859,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chilcas</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4771,6 +4976,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chilcas</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4883,6 +5093,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chilcas</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4993,6 +5208,11 @@
       <c r="AD44" t="inlineStr">
         <is>
           <t>UGEL LA MAR</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chilcas</t>
         </is>
       </c>
     </row>
@@ -5093,6 +5313,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Hualla</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5197,6 +5422,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Victor Fajardo</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5299,6 +5529,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huanta</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5401,6 +5636,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llochegua</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5503,6 +5743,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llochegua</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5615,6 +5860,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ninabamba</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5721,6 +5971,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pucacolpa</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5825,6 +6080,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pucacolpa</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5933,6 +6193,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pucacolpa</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6035,6 +6300,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6137,6 +6407,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6239,6 +6514,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6341,6 +6621,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6443,6 +6728,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6545,6 +6835,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6647,6 +6942,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6749,6 +7049,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6851,6 +7156,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan Bautista</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6953,6 +7263,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan Bautista</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7065,6 +7380,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sarhua</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7167,6 +7487,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7271,6 +7596,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7373,6 +7703,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7475,6 +7810,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Uchuraccay</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7577,6 +7917,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ayacucho</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7689,6 +8034,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD La Florida</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7801,6 +8151,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD La Florida</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7907,6 +8262,11 @@
       <c r="AD72" t="inlineStr">
         <is>
           <t>UGEL ESPINAR</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Coporaque</t>
         </is>
       </c>
     </row>
@@ -8001,6 +8361,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Inkawasi</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8093,6 +8458,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Inkawasi</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8185,6 +8555,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Inkawasi</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8277,6 +8652,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Inkawasi</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8381,6 +8761,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pallpata</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8485,6 +8870,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pallpata</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8583,6 +8973,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8681,6 +9076,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8779,6 +9179,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8877,6 +9282,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8973,6 +9383,11 @@
       <c r="AD83" t="inlineStr">
         <is>
           <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
     </row>
@@ -9073,6 +9488,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9169,6 +9589,11 @@
       <c r="AD85" t="inlineStr">
         <is>
           <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
     </row>
@@ -9263,6 +9688,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Huanca-Huanca</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9383,6 +9813,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huanuco</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9487,6 +9922,11 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llaylla</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9595,6 +10035,11 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llaylla</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9701,6 +10146,11 @@
       <c r="AD90" t="inlineStr">
         <is>
           <t>UGEL SATIPO</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llaylla</t>
         </is>
       </c>
     </row>
@@ -9807,6 +10257,11 @@
           <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Moche</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9915,6 +10370,11 @@
       <c r="AD92" t="inlineStr">
         <is>
           <t>UGEL 04 - TRUJILLO SUR ESTE</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Moche</t>
         </is>
       </c>
     </row>
@@ -10017,6 +10477,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10115,6 +10580,11 @@
       <c r="AD94" t="inlineStr">
         <is>
           <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
         </is>
       </c>
     </row>
@@ -10211,6 +10681,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 03 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10311,6 +10786,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10411,6 +10891,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10519,6 +11004,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huaral</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10627,6 +11117,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huaral</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10735,6 +11230,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huaral</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10841,6 +11341,11 @@
       <c r="AD101" t="inlineStr">
         <is>
           <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huaral</t>
         </is>
       </c>
     </row>
@@ -10945,6 +11450,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11057,6 +11567,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Jenaro Herrera</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11155,6 +11670,11 @@
           <t>UGEL PUTUMAYO</t>
         </is>
       </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Putumayo</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11253,6 +11773,11 @@
           <t>UGEL PUTUMAYO</t>
         </is>
       </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Putumayo</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11357,6 +11882,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Bellavista de la Union</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11453,6 +11983,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11565,6 +12100,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11677,6 +12217,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11789,6 +12334,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11901,6 +12451,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12011,6 +12566,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12123,6 +12683,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12235,6 +12800,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12347,6 +12917,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12459,6 +13034,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12563,6 +13143,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12673,6 +13258,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12793,6 +13383,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12903,6 +13498,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13015,6 +13615,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13127,6 +13732,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Elias Soplin Vargas</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE122"/>
+  <dimension ref="A1:AG122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,6 +568,16 @@
         </is>
       </c>
       <c r="AE1" t="inlineStr">
+        <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -678,6 +688,16 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
+          <t>88105 JUAN NOEL LASTRA/88105 JUAN NOEL LASTRA</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Comandante Noel</t>
         </is>
       </c>
@@ -785,6 +805,16 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>86628 CAPITAN FAP JOSE ABELARDO QUIÑONES</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -894,6 +924,16 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>CARLOS AUGUSTO SALAVERRY</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Paucas</t>
         </is>
       </c>
@@ -1001,6 +1041,16 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>89538 JUAN BAUTISTA ALVAREZ VERA/046</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -1108,6 +1158,16 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>89554/89554</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -1215,6 +1275,16 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>89556/89556/89556</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -1322,6 +1392,16 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -1429,6 +1509,16 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>86026 SANTA INES</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -1536,6 +1626,16 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -1649,6 +1749,16 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
       </c>
@@ -1761,6 +1871,16 @@
         </is>
       </c>
       <c r="AE12" t="inlineStr">
+        <is>
+          <t>475-3</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
@@ -1861,6 +1981,16 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>54481</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
       </c>
@@ -1973,6 +2103,16 @@
         </is>
       </c>
       <c r="AE14" t="inlineStr">
+        <is>
+          <t>475-23</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
@@ -2073,6 +2213,16 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>MARIO VARGAS LLOSA</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
       </c>
@@ -2184,6 +2334,16 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
       </c>
@@ -2300,6 +2460,16 @@
         </is>
       </c>
       <c r="AE17" t="inlineStr">
+        <is>
+          <t>54328</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tintay</t>
         </is>
@@ -2407,6 +2577,16 @@
         </is>
       </c>
       <c r="AE18" t="inlineStr">
+        <is>
+          <t>40705/40705/40705</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
@@ -2509,6 +2689,16 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
+          <t>40202 CHARLOTTE/40202 CHARLOTTE/40202 CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -2610,6 +2800,16 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA/40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA/40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -2711,6 +2911,16 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
+          <t>EL ALTIPLANO/EL ALTIPLANO</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -2812,6 +3022,16 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
+          <t>SANTO TORIBIO DE MOGROVEJO/SANTO TORIBIO DE MOGROVEJO/SANTO TORIBIO DE MOGROVEJO</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -2913,6 +3133,16 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
+          <t>JARDIN DEL COLCA/JARDIN DEL COLCA/JARDIN DEL COLCA</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -3020,6 +3250,16 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
+          <t>GENERAL TRINIDAD MORAN/310 GENERAL TRINIDAD MORAN/GENERAL TRINIDAD MORAN 38032</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3127,6 +3367,16 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
+          <t>38699 RAYAN</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3234,6 +3484,16 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
+          <t>38912</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3341,6 +3601,16 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
+          <t>432-28</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3448,6 +3718,16 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
+          <t>38564</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3555,6 +3835,16 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
+          <t>38724</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3662,6 +3952,16 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
+          <t>38864/38864</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3769,6 +4069,16 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
+          <t>425-17</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3876,6 +4186,16 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
+          <t>425-161</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -3985,6 +4305,16 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LOURDES/NUESTRA SEÑORA DE LOURDES/NUESTRA SEÑORA DE LOURDES</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -4092,6 +4422,16 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
+          <t>LOS LIBERTADORES/LOS LIBERTADORES/LOS LIBERTADORES/LOS LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -4199,6 +4539,16 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
+          <t>39007 SEÑOR DE AGONIA</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -4306,6 +4656,16 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
+          <t>38984-22 ALFREDO MENDOZA SALAZAR</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -4413,6 +4773,16 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
+          <t>COAR AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -4520,6 +4890,16 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
+          <t>38582 ABRAHAM VALDELOMAR/38582 ABRAHAM VALDELOMAR/38582 ABRAHAM VALDELOMAR</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -4627,6 +5007,16 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
+          <t>38984-23</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -4744,6 +5134,16 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
+          <t>38374</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
       </c>
@@ -4861,6 +5261,16 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
+          <t>38375</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
       </c>
@@ -4978,6 +5388,16 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
+          <t>38376</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
       </c>
@@ -5095,6 +5515,16 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
+          <t>38413</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
       </c>
@@ -5211,6 +5641,16 @@
         </is>
       </c>
       <c r="AE44" t="inlineStr">
+        <is>
+          <t>38720</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
@@ -5315,6 +5755,16 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
+          <t>38478 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Hualla</t>
         </is>
       </c>
@@ -5424,6 +5874,16 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
+          <t>BASILIO AUQUI</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Victor Fajardo</t>
         </is>
       </c>
@@ -5531,6 +5991,16 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
+          <t>38878</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huanta</t>
         </is>
       </c>
@@ -5638,6 +6108,16 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
+          <t>38645</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Llochegua</t>
         </is>
       </c>
@@ -5745,6 +6225,16 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
+          <t>VILLA MEJORADA</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Llochegua</t>
         </is>
       </c>
@@ -5862,6 +6352,16 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
+          <t>38368</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ninabamba</t>
         </is>
       </c>
@@ -5973,6 +6473,16 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
+          <t>38321 SEÑOR DE LA DIVINA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pucacolpa</t>
         </is>
       </c>
@@ -6082,6 +6592,16 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
+          <t>38552/38552</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pucacolpa</t>
         </is>
       </c>
@@ -6195,6 +6715,16 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
+          <t>38679/38679</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pucacolpa</t>
         </is>
       </c>
@@ -6302,6 +6832,16 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -6409,6 +6949,16 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
+          <t>24296 TODAS LAS SANGRES DEL PERU</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -6516,6 +7066,16 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
+          <t>971 LOS ANGELITOS</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -6623,6 +7183,16 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -6730,6 +7300,16 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
+          <t>25512</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -6837,6 +7417,16 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -6944,6 +7534,16 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -7051,6 +7651,16 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
+          <t>25513</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -7158,6 +7768,16 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
+          <t>432-50</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan Bautista</t>
         </is>
       </c>
@@ -7265,6 +7885,16 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
+          <t>432-82</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan Bautista</t>
         </is>
       </c>
@@ -7382,6 +8012,16 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
+          <t>430-5</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sarhua</t>
         </is>
       </c>
@@ -7489,6 +8129,16 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
+          <t>38978</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -7598,6 +8248,16 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
+          <t>JOSE ABELARDO QUIÑONES</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -7705,6 +8365,16 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
+          <t>432-58</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -7812,6 +8482,16 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
+          <t>ARTEMIO SANCHEZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Uchuraccay</t>
         </is>
       </c>
@@ -7919,6 +8599,16 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
+          <t>LUIS A SANCHEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
       </c>
@@ -8036,6 +8726,16 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
+          <t>82748</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD La Florida</t>
         </is>
       </c>
@@ -8153,6 +8853,16 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
+          <t>MARIANO MELGAR</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD La Florida</t>
         </is>
       </c>
@@ -8265,6 +8975,16 @@
         </is>
       </c>
       <c r="AE72" t="inlineStr">
+        <is>
+          <t>56217/56217</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Coporaque</t>
         </is>
@@ -8363,6 +9083,16 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
+          <t>50262/50262</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Inkawasi</t>
         </is>
       </c>
@@ -8460,6 +9190,16 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
+          <t>50263</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Inkawasi</t>
         </is>
       </c>
@@ -8557,6 +9297,16 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
+          <t>50744/50744/50744</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Inkawasi</t>
         </is>
       </c>
@@ -8654,6 +9404,16 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
+          <t>SAN MARTIN/50885</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Inkawasi</t>
         </is>
       </c>
@@ -8763,6 +9523,16 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
+          <t>56192 SIMON BOLIVAR/56192 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pallpata</t>
         </is>
       </c>
@@ -8872,6 +9642,16 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
+          <t>501393</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pallpata</t>
         </is>
       </c>
@@ -8975,6 +9755,16 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
+          <t>38831/38831</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -9078,6 +9868,16 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
+          <t>38838 CAPITAN FAP JOSE ABELARDO QUIÑONES GONZALES</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -9181,6 +9981,16 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
+          <t>LA VICTORIA/LA VICTORIA/LA VICTORIA</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -9284,6 +10094,16 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
+          <t>38990-A MARAVILLA/38990-A MARAVILLA/38990-A MARAVILLA</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -9386,6 +10206,16 @@
         </is>
       </c>
       <c r="AE83" t="inlineStr">
+        <is>
+          <t>38776/38776</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -9490,6 +10320,16 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
+          <t>UNION KINKORI/UNION KINKORI</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -9592,6 +10432,16 @@
         </is>
       </c>
       <c r="AE85" t="inlineStr">
+        <is>
+          <t>1369 ISAAC NEWTON/1369 ISAAC NEWTON</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -9690,6 +10540,16 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
+          <t>36271</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Huanca-Huanca</t>
         </is>
       </c>
@@ -9815,6 +10675,16 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
+          <t>32942 PILLCO MOZO/32942 PILLCO MOZO/32942 PILLCO MOZO</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huanuco</t>
         </is>
       </c>
@@ -9924,6 +10794,16 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
+          <t>AGROINDUSTRIAL/AGROINDUSTRIAL/AGROINDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
       </c>
@@ -10037,6 +10917,16 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
+          <t>30664</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
       </c>
@@ -10149,6 +11039,16 @@
         </is>
       </c>
       <c r="AE90" t="inlineStr">
+        <is>
+          <t>JORGE CHAVEZ</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
@@ -10259,6 +11159,16 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
+          <t>1613 MI DULCE HOGAR</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
       </c>
@@ -10373,6 +11283,16 @@
         </is>
       </c>
       <c r="AE92" t="inlineStr">
+        <is>
+          <t>80082 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
@@ -10479,6 +11399,16 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
+          <t>209 MELVA CEDILIA ROJAS ALIAGA</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -10583,6 +11513,16 @@
         </is>
       </c>
       <c r="AE94" t="inlineStr">
+        <is>
+          <t>1285/1285</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
         </is>
@@ -10683,6 +11623,16 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
+          <t>16 VIRGEN DE LOURDES</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 03 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -10788,6 +11738,16 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
+          <t>129 YAMAGUCHI/129 YAMAGUCHI/129 YAMAGUCHI/129 YAMAGUCHI</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -10893,6 +11853,16 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
+          <t>DIVINA MISERICORDIA/DIVINA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -11006,6 +11976,16 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
+          <t>546 SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
       </c>
@@ -11119,6 +12099,16 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
+          <t>21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
       </c>
@@ -11232,6 +12222,16 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
+          <t>20407/20407</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
       </c>
@@ -11344,6 +12344,16 @@
         </is>
       </c>
       <c r="AE101" t="inlineStr">
+        <is>
+          <t>02 JUAN YSHIZAWA YSHIZAWA/02 JUAN YSHIZAWA YSHIZAWA</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
@@ -11452,6 +12462,16 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
@@ -11569,6 +12589,16 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Jenaro Herrera</t>
         </is>
       </c>
@@ -11672,6 +12702,16 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
+          <t>166 MARIA ANGELICA SOUSA MANIHUARI</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Putumayo</t>
         </is>
       </c>
@@ -11775,6 +12815,16 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Putumayo</t>
         </is>
       </c>
@@ -11884,6 +12934,16 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Bellavista de la Union</t>
         </is>
       </c>
@@ -11985,6 +13045,16 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -12102,6 +13172,16 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -12219,6 +13299,16 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
+          <t>00910</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -12336,6 +13426,16 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
+          <t>00849</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -12453,6 +13553,16 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
+          <t>00828/00828</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -12568,6 +13678,16 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
+          <t>00821/00821</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -12685,6 +13805,16 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
+          <t>00123</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -12802,6 +13932,16 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
+          <t>00875</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -12919,6 +14059,16 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
+          <t>1283/1283</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -13036,6 +14186,16 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
+          <t>313 JEHOVA ES MI PASTOR</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -13145,6 +14305,16 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
+          <t>DIVINO MAESTRO</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -13260,6 +14430,16 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -13385,6 +14565,16 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
+          <t>317/317</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -13500,6 +14690,16 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
+          <t>00170</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -13617,6 +14817,16 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
+          <t>EMAUS/EMAUS</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>
@@ -13734,6 +14944,16 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
+          <t>00623/00623</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
       </c>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
@@ -419,92 +419,92 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Provincia</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Nombre de la I.E.</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>1, Cantidad de Módulos prefabricados - aula</t>
+          <t>1_cantidad_de_modulos_prefabricados_aula</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>1, Año de intervención de Módulos prefabricados - aula</t>
+          <t>1_ano_de_intervencion_de_modulos_prefabricados_aula</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2, Cantidad de Módulos prefabricados - otros ambientes</t>
+          <t>2_cantidad_de_modulos_prefabricados_otros_ambientes</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2, Describir los ambientes intervenidos</t>
+          <t>2_describir_los_ambientes_intervenidos</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2, Año de intervención de Módulos prefabricados - otros ambientes</t>
+          <t>2_ano_de_intervencion_de_modulos_prefabricados_otros_ambient</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>3, Cantidad de Módulos prefabricados - SSHH</t>
+          <t>3_cantidad_de_modulos_prefabricados_sshh</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>3, Año de intervención de Módulos prefabricados - aula</t>
+          <t>3_ano_de_intervencion_de_modulos_prefabricados_aula</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>4, Cantidad de Módulos prefabricados - SSBB (Biodigestores/tanques provisionales u otros)</t>
+          <t>4_cantidad_de_modulos_prefabricados_ssbb_biodigestores_tanqu</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>4, Año de intervención de Módulos prefabricados - aula</t>
+          <t>4_ano_de_intervencion_de_modulos_prefabricados_aula</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Monto contractual total (S/)</t>
+          <t>monto_contractual_total_s</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>REMITENTE</t>
+          <t>remitente</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -514,37 +514,37 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>nan (1)</t>
+          <t>nan_1</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>nan (2)</t>
+          <t>nan_2</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>nan (3)</t>
+          <t>nan_3</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>nan (4)</t>
+          <t>nan_4</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>departamento_2</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>provincia_2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>distrito_2</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">

--- a/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_anexo2_a.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG122"/>
+  <dimension ref="A1:AA122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,70 +514,40 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>nan_1</t>
+          <t>nan_2</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>nan_2</t>
+          <t>nan_3</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>nan_3</t>
+          <t>centro_poblado</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>nan_4</t>
+          <t>ubigeo</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>departamento_2</t>
+          <t>dre</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>provincia_2</t>
+          <t>ugel</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>distrito_2</t>
+          <t>area</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
-        <is>
-          <t>centro_poblado</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ubigeo</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>dre</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>ugel</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>nombre_ie_2</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -649,54 +619,32 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>PUERTO DE CASMA</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>020803</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>CASMA</t>
+          <t>UGEL CASMA</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>COMANDANTE NOEL</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
-        <is>
-          <t>PUERTO DE CASMA</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>020803</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>UGEL CASMA</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>88105 JUAN NOEL LASTRA/88105 JUAN NOEL LASTRA</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Comandante Noel</t>
         </is>
@@ -766,54 +714,32 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>MANCOS</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>022003</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>MANCOS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
-        <is>
-          <t>MANCOS</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>022003</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>UGEL YUNGAY</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>86628 CAPITAN FAP JOSE ABELARDO QUIÑONES</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -885,54 +811,32 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>VISCAS</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>021010</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>HUARI</t>
+          <t>UGEL HUARI</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>PAUCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
-        <is>
-          <t>VISCAS</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>021010</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>UGEL HUARI</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>CARLOS AUGUSTO SALAVERRY</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Paucas</t>
         </is>
@@ -1002,54 +906,32 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>OCUPAMPA</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>022005</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>QUILLO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
-        <is>
-          <t>OCUPAMPA</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>022005</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>UGEL YUNGAY</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>89538 JUAN BAUTISTA ALVAREZ VERA/046</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -1119,54 +1001,32 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>PAÑOPAMPA</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>022005</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>QUILLO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
-        <is>
-          <t>PAÑOPAMPA</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>022005</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>UGEL YUNGAY</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>89554/89554</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -1236,54 +1096,32 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>AUNAPAMPA</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>022005</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>QUILLO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
-        <is>
-          <t>AUNAPAMPA</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>022005</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>UGEL YUNGAY</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>89556/89556/89556</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -1353,54 +1191,32 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>CAYASBAMBA</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>022001</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
-        <is>
-          <t>CAYASBAMBA</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>022001</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>UGEL YUNGAY</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -1470,54 +1286,32 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>YUNGAY</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>022001</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
-        <is>
-          <t>YUNGAY</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>022001</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>UGEL YUNGAY</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>86026 SANTA INES</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -1587,54 +1381,32 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SHACSHA</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>022001</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>YUNGAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
-        <is>
-          <t>SHACSHA</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>022001</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>UGEL YUNGAY</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -1710,54 +1482,32 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>COCHARCAS</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>030603</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>DRE APURIMAC</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>CHINCHEROS</t>
+          <t>UGEL CHINCHEROS</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>COCHARCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
-        <is>
-          <t>COCHARCAS</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>030603</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>DRE APURIMAC</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>UGEL CHINCHEROS</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
@@ -1833,54 +1583,32 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SAÑOCC</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>030603</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>DRE APURIMAC</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>CHINCHEROS</t>
+          <t>UGEL CHINCHEROS</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>COCHARCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
-        <is>
-          <t>SAÑOCC</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>030603</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>DRE APURIMAC</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>UGEL CHINCHEROS</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>475-3</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
@@ -1942,54 +1670,32 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>OSCOLLO</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>030603</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>DRE APURIMAC</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>CHINCHEROS</t>
+          <t>UGEL CHINCHEROS</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>COCHARCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
-        <is>
-          <t>OSCOLLO</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>030603</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>DRE APURIMAC</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>UGEL CHINCHEROS</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>54481</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
@@ -2065,54 +1771,32 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>OSCOLLO</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>030603</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>DRE APURIMAC</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>CHINCHEROS</t>
+          <t>UGEL CHINCHEROS</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>COCHARCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
-        <is>
-          <t>OSCOLLO</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>030603</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>DRE APURIMAC</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>UGEL CHINCHEROS</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>475-23</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
@@ -2174,54 +1858,32 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>OSCOLLO</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>030603</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>DRE APURIMAC</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>CHINCHEROS</t>
+          <t>UGEL CHINCHEROS</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>COCHARCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
-        <is>
-          <t>OSCOLLO</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>030603</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>DRE APURIMAC</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>UGEL CHINCHEROS</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>MARIO VARGAS LLOSA</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
@@ -2295,54 +1957,32 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ACHIBAMBA</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>030603</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>DRE APURIMAC</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>CHINCHEROS</t>
+          <t>UGEL CHINCHEROS</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>COCHARCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
-        <is>
-          <t>ACHIBAMBA</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>030603</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>DRE APURIMAC</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>UGEL CHINCHEROS</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>904</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cocharcas</t>
         </is>
@@ -2422,54 +2062,32 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SAN MATEO</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>030415</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>DRE APURIMAC</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>AYMARAES</t>
+          <t>UGEL AYMARAES</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>TINTAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
-        <is>
-          <t>SAN MATEO</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>030415</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>DRE APURIMAC</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>UGEL AYMARAES</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>54328</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tintay</t>
         </is>
@@ -2539,54 +2157,32 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>PERUARBO</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>040104</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>CERRO COLORADO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
-        <is>
-          <t>PERUARBO</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>040104</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>UGEL AREQUIPA NORTE</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>40705/40705/40705</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
@@ -2650,54 +2246,32 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>CIUDAD DE DIOS</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>040128</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>YURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
-        <is>
-          <t>CIUDAD DE DIOS</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>040128</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>UGEL AREQUIPA NORTE</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>40202 CHARLOTTE/40202 CHARLOTTE/40202 CHARLOTTE</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
@@ -2761,54 +2335,32 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>CAMINEROS EMPLEADOS</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>040128</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>YURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
-        <is>
-          <t>CAMINEROS EMPLEADOS</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>040128</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>UGEL AREQUIPA NORTE</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA/40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA/40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
@@ -2872,54 +2424,32 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>CONO NORTE</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>040128</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>YURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
-        <is>
-          <t>CONO NORTE</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>040128</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>UGEL AREQUIPA NORTE</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>EL ALTIPLANO/EL ALTIPLANO</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
@@ -2983,54 +2513,32 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>APIAAR</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>040128</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>YURA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
-        <is>
-          <t>APIAAR</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>040128</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>UGEL AREQUIPA NORTE</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>SANTO TORIBIO DE MOGROVEJO/SANTO TORIBIO DE MOGROVEJO/SANTO TORIBIO DE MOGROVEJO</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
@@ -3094,54 +2602,32 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>JARDIN DEL COLCA</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>040128</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>YURA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
-        <is>
-          <t>JARDIN DEL COLCA</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>040128</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>UGEL AREQUIPA NORTE</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>JARDIN DEL COLCA/JARDIN DEL COLCA/JARDIN DEL COLCA</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
@@ -3211,54 +2697,32 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>ACOCRO</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>050102</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>ACOCRO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
-        <is>
-          <t>ACOCRO</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>050102</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>GENERAL TRINIDAD MORAN/310 GENERAL TRINIDAD MORAN/GENERAL TRINIDAD MORAN 38032</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -3328,54 +2792,32 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE RAYAN</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>050102</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>ACOCRO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE RAYAN</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>050102</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>38699 RAYAN</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -3445,54 +2887,32 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>ACCO</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>050102</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>ACOCRO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
-        <is>
-          <t>ACCO</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>050102</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>38912</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -3562,54 +2982,32 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>HACIENDA HUAMANCONA</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>050103</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>ACOS VINCHOS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
-        <is>
-          <t>HACIENDA HUAMANCONA</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>050103</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>432-28</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -3679,54 +3077,32 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>ISOCCASA</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>050510</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>ANCHIHUAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
-        <is>
-          <t>ISOCCASA</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>050510</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>38564</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -3796,54 +3172,32 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>BUENA GANA</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>050510</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>ANCHIHUAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
-        <is>
-          <t>BUENA GANA</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>050510</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>38724</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -3913,54 +3267,32 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>SAN JOSE</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>050510</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>ANCHIHUAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
-        <is>
-          <t>SAN JOSE</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>050510</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>38864/38864</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4030,54 +3362,32 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SAN JOSE</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>050510</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>ANCHIHUAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
-        <is>
-          <t>SAN JOSE</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>050510</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>425-17</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4147,54 +3457,32 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>CCOLLPAPAMPA</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>050510</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>ANCHIHUAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
-        <is>
-          <t>CCOLLPAPAMPA</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>050510</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>425-161</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4266,54 +3554,32 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>050116</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
-        <is>
-          <t>SANTA ELENA</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>NUESTRA SEÑORA DE LOURDES/NUESTRA SEÑORA DE LOURDES/NUESTRA SEÑORA DE LOURDES</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4383,54 +3649,32 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>LOS LIBERTADORES/LOS LIBERTADORES/LOS LIBERTADORES/LOS LIBERTADORES</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4500,54 +3744,32 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>39007 SEÑOR DE AGONIA</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4617,54 +3839,32 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>MOLLEPATA</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
-        <is>
-          <t>MOLLEPATA</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>38984-22 ALFREDO MENDOZA SALAZAR</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4734,54 +3934,32 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>COAR AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4851,54 +4029,32 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>VISTA ALEGRE</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>050104</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
-        <is>
-          <t>VISTA ALEGRE</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>050104</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>38582 ABRAHAM VALDELOMAR/38582 ABRAHAM VALDELOMAR/38582 ABRAHAM VALDELOMAR</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -4968,54 +4124,32 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>YANAMA</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>050104</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
-        <is>
-          <t>YANAMA</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>050104</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>38984-23</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -5095,54 +4229,32 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>CHILCAS</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>050504</t>
+        </is>
+      </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>CHILCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
-        <is>
-          <t>CHILCAS</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>050504</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>38374</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
@@ -5222,54 +4334,32 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>ESCCANA</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>050504</t>
+        </is>
+      </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>CHILCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
-        <is>
-          <t>ESCCANA</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>050504</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>38375</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
@@ -5349,54 +4439,32 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>RUMI RUMI</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>050504</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>CHILCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
-        <is>
-          <t>RUMI RUMI</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>050504</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>38376</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
@@ -5476,54 +4544,32 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>RETAMA</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>050504</t>
+        </is>
+      </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>CHILCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
-        <is>
-          <t>RETAMA</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>050504</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>38413</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
@@ -5603,54 +4649,32 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>QOYAMA</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>050504</t>
+        </is>
+      </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>CHILCAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
-        <is>
-          <t>QOYAMA</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>050504</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>38720</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Chilcas</t>
         </is>
@@ -5716,54 +4740,32 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>HUALLA / SAN PEDRO DE HUAYA</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>051010</t>
+        </is>
+      </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO</t>
+          <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>HUALLA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
-        <is>
-          <t>HUALLA / SAN PEDRO DE HUAYA</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>051010</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>UGEL VÍCTOR FAJARDO</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>38478 SAN MARTIN DE PORRES</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Hualla</t>
         </is>
@@ -5835,54 +4837,32 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>HUANCAPI</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>051001</t>
+        </is>
+      </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO</t>
+          <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>HUANCAPI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
-        <is>
-          <t>HUANCAPI</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>051001</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>UGEL VÍCTOR FAJARDO</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>BASILIO AUQUI</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Victor Fajardo</t>
         </is>
@@ -5952,54 +4932,32 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>PATASUCRO</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>050401</t>
+        </is>
+      </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UGEL HUANTA</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
-        <is>
-          <t>PATASUCRO</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>050401</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>UGEL HUANTA</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>38878</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huanta</t>
         </is>
@@ -6069,54 +5027,32 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>050408</t>
+        </is>
+      </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UGEL HUANTA</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
-        <is>
-          <t>LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>050408</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>UGEL HUANTA</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>38645</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Llochegua</t>
         </is>
@@ -6186,54 +5122,32 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>VILLA MEJORADA</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>050408</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UGEL HUANTA</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
-        <is>
-          <t>VILLA MEJORADA</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>050408</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>UGEL HUANTA</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>VILLA MEJORADA</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Llochegua</t>
         </is>
@@ -6313,54 +5227,32 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>CHAQO</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>050514</t>
+        </is>
+      </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>NINABAMBA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
-        <is>
-          <t>CHAQO</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>050514</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>UGEL LA MAR</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>38368</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Ninabamba</t>
         </is>
@@ -6434,54 +5326,32 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>CHACHASPATA</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>050411</t>
+        </is>
+      </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UGEL HUANTA</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
-        <is>
-          <t>CHACHASPATA</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>050411</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>UGEL HUANTA</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>38321 SEÑOR DE LA DIVINA MISERICORDIA</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pucacolpa</t>
         </is>
@@ -6553,54 +5423,32 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>HUARCATAN</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>050411</t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UGEL HUANTA</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
-        <is>
-          <t>HUARCATAN</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>050411</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>UGEL HUANTA</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>38552/38552</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pucacolpa</t>
         </is>
@@ -6676,54 +5524,32 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TAMBOPACOCHA</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>050411</t>
+        </is>
+      </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UGEL HUANTA</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
-        <is>
-          <t>TAMBOPACOCHA</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>050411</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>UGEL HUANTA</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>38679/38679</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pucacolpa</t>
         </is>
@@ -6793,54 +5619,32 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>050705</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>PARINACOCHAS</t>
+          <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>PULLO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>050705</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>UGEL PARINACOCHAS</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -6910,54 +5714,32 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>050705</t>
+        </is>
+      </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>PARINACOCHAS</t>
+          <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>PULLO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>050705</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>UGEL PARINACOCHAS</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>24296 TODAS LAS SANGRES DEL PERU</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -7027,54 +5809,32 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>050705</t>
+        </is>
+      </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>PARINACOCHAS</t>
+          <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>PULLO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>050705</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>UGEL PARINACOCHAS</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>971 LOS ANGELITOS</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -7144,54 +5904,32 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>050705</t>
+        </is>
+      </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>PARINACOCHAS</t>
+          <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>PULLO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>050705</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>UGEL PARINACOCHAS</t>
-        </is>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -7261,54 +5999,32 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>050705</t>
+        </is>
+      </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>PARINACOCHAS</t>
+          <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>PULLO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>050705</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>UGEL PARINACOCHAS</t>
-        </is>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>25512</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -7378,54 +6094,32 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>050705</t>
+        </is>
+      </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>PARINACOCHAS</t>
+          <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>PULLO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>050705</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>UGEL PARINACOCHAS</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -7495,54 +6189,32 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>050705</t>
+        </is>
+      </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>PARINACOCHAS</t>
+          <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>PULLO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>050705</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>UGEL PARINACOCHAS</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -7612,54 +6284,32 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>RELAVE</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>050705</t>
+        </is>
+      </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>PARINACOCHAS</t>
+          <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>PULLO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
-        <is>
-          <t>RELAVE</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>050705</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>UGEL PARINACOCHAS</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>25513</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -7729,54 +6379,32 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>050110</t>
+        </is>
+      </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>050110</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>432-50</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
         <is>
           <t>Anexo 2 - MD San Juan Bautista</t>
         </is>
@@ -7846,54 +6474,32 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>050110</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>050110</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>432-82</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
         <is>
           <t>Anexo 2 - MD San Juan Bautista</t>
         </is>
@@ -7973,54 +6579,32 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TOMANCCA</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>051011</t>
+        </is>
+      </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO</t>
+          <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>SARHUA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
-        <is>
-          <t>TOMANCCA</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>051011</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>UGEL VÍCTOR FAJARDO</t>
-        </is>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>430-5</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG64" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Sarhua</t>
         </is>
@@ -8090,54 +6674,32 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>PAUCHO</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>050112</t>
+        </is>
+      </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>SOCOS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
-        <is>
-          <t>PAUCHO</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>050112</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>38978</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -8209,54 +6771,32 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE COCHABAMBA</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>050112</t>
+        </is>
+      </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>SOCOS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
-        <is>
-          <t>SANTA ROSA DE COCHABAMBA</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>050112</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>JOSE ABELARDO QUIÑONES</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -8326,54 +6866,32 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>UCHUIPAMPA</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>050113</t>
+        </is>
+      </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>TAMBILLO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
-        <is>
-          <t>UCHUIPAMPA</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>050113</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>432-58</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -8443,54 +6961,32 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>QATUPATA</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>050410</t>
+        </is>
+      </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UGEL HUANTA</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>UCHURACCAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
-        <is>
-          <t>QATUPATA</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>050410</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>UGEL HUANTA</t>
-        </is>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>ARTEMIO SANCHEZ LOPEZ</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Uchuraccay</t>
         </is>
@@ -8560,54 +7056,32 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>OCCOLLO</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>050114</t>
+        </is>
+      </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>HUAMANGA</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>VINCHOS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
-        <is>
-          <t>OCCOLLO</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>050114</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>DRE AYACUCHO</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>UGEL HUAMANGA</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>LUIS A SANCHEZ SANCHEZ</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ayacucho</t>
         </is>
@@ -8687,54 +7161,32 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>061106</t>
+        </is>
+      </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>DRE CAJAMARCA</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>LA FLORIDA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
-        <is>
-          <t>LA FLORIDA</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>061106</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>DRE CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>UGEL SAN MIGUEL</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>82748</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
         <is>
           <t>Anexo 2 - MD La Florida</t>
         </is>
@@ -8814,54 +7266,32 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>LA LAJA</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>061106</t>
+        </is>
+      </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>DRE CAJAMARCA</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>LA FLORIDA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
-        <is>
-          <t>LA LAJA</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>061106</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>DRE CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>UGEL SAN MIGUEL</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>MARIANO MELGAR</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
         <is>
           <t>Anexo 2 - MD La Florida</t>
         </is>
@@ -8937,54 +7367,32 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TAHUAPALCA</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>080803</t>
+        </is>
+      </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>ESPINAR</t>
+          <t>UGEL ESPINAR</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>COPORAQUE</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
-        <is>
-          <t>TAHUAPALCA</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>080803</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>UGEL ESPINAR</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>56217/56217</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Coporaque</t>
         </is>
@@ -9044,54 +7452,32 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>ERAPATA</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>080911</t>
+        </is>
+      </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>INKAWASI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
-        <is>
-          <t>ERAPATA</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>080911</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>UGEL LA CONVENCIÓN</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>50262/50262</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Inkawasi</t>
         </is>
@@ -9151,54 +7537,32 @@
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>INCAHUASI</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>080911</t>
+        </is>
+      </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>INKAWASI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
-        <is>
-          <t>INCAHUASI</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>080911</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>UGEL LA CONVENCIÓN</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>50263</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Inkawasi</t>
         </is>
@@ -9258,54 +7622,32 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>AMAYBAMBA</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>080911</t>
+        </is>
+      </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>INKAWASI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
-        <is>
-          <t>AMAYBAMBA</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>080911</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>UGEL LA CONVENCIÓN</t>
-        </is>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>50744/50744/50744</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Inkawasi</t>
         </is>
@@ -9365,54 +7707,32 @@
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>080911</t>
+        </is>
+      </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>INKAWASI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>080911</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>UGEL LA CONVENCIÓN</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>SAN MARTIN/50885</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Inkawasi</t>
         </is>
@@ -9484,54 +7804,32 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>HECTOR TEJADA</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>080805</t>
+        </is>
+      </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>ESPINAR</t>
+          <t>UGEL ESPINAR</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>PALLPATA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
-        <is>
-          <t>HECTOR TEJADA</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>080805</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>UGEL ESPINAR</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>56192 SIMON BOLIVAR/56192 SIMON BOLIVAR</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pallpata</t>
         </is>
@@ -9603,54 +7901,32 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>JAPO</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>080805</t>
+        </is>
+      </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>ESPINAR</t>
+          <t>UGEL ESPINAR</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>PALLPATA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
-        <is>
-          <t>JAPO</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>080805</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>UGEL ESPINAR</t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>501393</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG78" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pallpata</t>
         </is>
@@ -9716,54 +7992,32 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>QUISTO VALLE</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>080910</t>
+        </is>
+      </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
-        <is>
-          <t>QUISTO VALLE</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>080910</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>UGEL PICHARI-KIMBIRI</t>
-        </is>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>38831/38831</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -9829,54 +8083,32 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>CCATUN RUMI</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>080910</t>
+        </is>
+      </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
-        <is>
-          <t>CCATUN RUMI</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>080910</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>UGEL PICHARI-KIMBIRI</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>38838 CAPITAN FAP JOSE ABELARDO QUIÑONES GONZALES</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -9942,54 +8174,32 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>PICHARI</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>080910</t>
+        </is>
+      </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
-        <is>
-          <t>PICHARI</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>080910</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD81" t="inlineStr">
-        <is>
-          <t>UGEL PICHARI-KIMBIRI</t>
-        </is>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>LA VICTORIA/LA VICTORIA/LA VICTORIA</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG81" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -10055,54 +8265,32 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>PICHARI</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>080910</t>
+        </is>
+      </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
-        <is>
-          <t>PICHARI</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>080910</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>UGEL PICHARI-KIMBIRI</t>
-        </is>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>38990-A MARAVILLA/38990-A MARAVILLA/38990-A MARAVILLA</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG82" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -10168,54 +8356,32 @@
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>OTARI SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>080910</t>
+        </is>
+      </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
-        <is>
-          <t>OTARI SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>080910</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>UGEL PICHARI-KIMBIRI</t>
-        </is>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>38776/38776</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -10281,54 +8447,32 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>UNION KINKORI</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>080910</t>
+        </is>
+      </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
-        <is>
-          <t>UNION KINKORI</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>080910</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>UGEL PICHARI-KIMBIRI</t>
-        </is>
-      </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>UNION KINKORI/UNION KINKORI</t>
-        </is>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG84" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -10394,54 +8538,32 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>PICHARI</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>080910</t>
+        </is>
+      </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
-        <is>
-          <t>PICHARI</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>080910</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>UGEL PICHARI-KIMBIRI</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>1369 ISAAC NEWTON/1369 ISAAC NEWTON</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -10501,54 +8623,32 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>CCARAPA</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>090307</t>
+        </is>
+      </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>DRE HUANCAVELICA</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>ANGARAES</t>
+          <t>UGEL ANGARAES</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>HUANCA-HUANCA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
-        <is>
-          <t>CCARAPA</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>090307</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>DRE HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>UGEL ANGARAES</t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>36271</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Huanca-Huanca</t>
         </is>
@@ -10636,54 +8736,32 @@
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>MARABAMBA</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>DRE HUANUCO</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>UGEL HUÁNUCO</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
-        <is>
-          <t>MARABAMBA</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>DRE HUANUCO</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>UGEL HUÁNUCO</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>32942 PILLCO MOZO/32942 PILLCO MOZO/32942 PILLCO MOZO</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huanuco</t>
         </is>
@@ -10755,54 +8833,32 @@
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>BELEN</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>120603</t>
+        </is>
+      </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>DRE JUNIN</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>SATIPO</t>
+          <t>UGEL SATIPO</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>LLAYLLA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
-        <is>
-          <t>BELEN</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>120603</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>DRE JUNIN</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>UGEL SATIPO</t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>AGROINDUSTRIAL/AGROINDUSTRIAL/AGROINDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
@@ -10878,54 +8934,32 @@
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SANTA CLARA</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>120603</t>
+        </is>
+      </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>DRE JUNIN</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>SATIPO</t>
+          <t>UGEL SATIPO</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>LLAYLLA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
-        <is>
-          <t>SANTA CLARA</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>120603</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>DRE JUNIN</t>
-        </is>
-      </c>
-      <c r="AD89" t="inlineStr">
-        <is>
-          <t>UGEL SATIPO</t>
-        </is>
-      </c>
-      <c r="AE89" t="inlineStr">
-        <is>
-          <t>30664</t>
-        </is>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG89" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
@@ -11001,54 +9035,32 @@
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>TEORIA</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>120603</t>
+        </is>
+      </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>DRE JUNIN</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>SATIPO</t>
+          <t>UGEL SATIPO</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>LLAYLLA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
-        <is>
-          <t>TEORIA</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>120603</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>DRE JUNIN</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>UGEL SATIPO</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>JORGE CHAVEZ</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
@@ -11115,59 +9127,37 @@
       </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>S/ 17,71237</t>
+        </is>
+      </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>S/ 17,71237</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr"/>
+          <t>MOCHE</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>130107</t>
+        </is>
+      </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
-        <is>
-          <t>MOCHE</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>GRE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
-        </is>
-      </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>1613 MI DULCE HOGAR</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
@@ -11237,62 +9227,40 @@
         </is>
       </c>
       <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="n">
+      <c r="T92" t="n">
         <v>2021</v>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>S/ 73,09734</t>
+        </is>
+      </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>S/ 73,09734</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr"/>
+          <t>CURVA DE SUN</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>130107</t>
+        </is>
+      </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
-        <is>
-          <t>CURVA DE SUN</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>130107</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>GRE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="AD92" t="inlineStr">
-        <is>
-          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
-        </is>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>80082 SAN FRANCISCO DE ASIS</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG92" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
@@ -11360,54 +9328,32 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>ALFA Y OMEGA</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
+      </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
-        <is>
-          <t>ALFA Y OMEGA</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>209 MELVA CEDILIA ROJAS ALIAGA</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG93" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
         </is>
@@ -11475,54 +9421,32 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
+      </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
-        <is>
-          <t>VITARTE</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AD94" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>1285/1285</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG94" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
         </is>
@@ -11584,54 +9508,32 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>LIMA CERCADO</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>150101</t>
+        </is>
+      </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>UGEL 03 BREÑA</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
-        <is>
-          <t>LIMA CERCADO</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>UGEL 03 BREÑA</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>16 VIRGEN DE LOURDES</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 03 - LIMA METROPOLITANA</t>
         </is>
@@ -11699,54 +9601,32 @@
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>150137</t>
+        </is>
+      </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>SANTA ANITA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>129 YAMAGUCHI/129 YAMAGUCHI/129 YAMAGUCHI/129 YAMAGUCHI</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 06 - LIMA METROPOLITANA</t>
         </is>
@@ -11814,54 +9694,32 @@
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>VILLA EL SALVADOR</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>DIVINA MISERICORDIA/DIVINA MISERICORDIA</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG97" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
         </is>
@@ -11937,54 +9795,32 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>150601</t>
+        </is>
+      </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
-        <is>
-          <t>HUARAL</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>150601</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>DRE LIMA PROVINCIAS</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>546 SAN ANTONIO</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
@@ -12060,54 +9896,32 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>HUANDO</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>150601</t>
+        </is>
+      </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
-        <is>
-          <t>HUANDO</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>150601</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>DRE LIMA PROVINCIAS</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE</t>
-        </is>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG99" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
@@ -12183,54 +9997,32 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>GARCIA ALONSO</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>150601</t>
+        </is>
+      </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
-        <is>
-          <t>GARCIA ALONSO</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>150601</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>DRE LIMA PROVINCIAS</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>20407/20407</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
@@ -12306,54 +10098,32 @@
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>150601</t>
+        </is>
+      </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
-        <is>
-          <t>HUARAL</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>150601</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>DRE LIMA PROVINCIAS</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>02 JUAN YSHIZAWA YSHIZAWA/02 JUAN YSHIZAWA YSHIZAWA</t>
-        </is>
-      </c>
-      <c r="AF101" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG101" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
@@ -12423,54 +10193,32 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>MAZO</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>150812</t>
+        </is>
+      </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>HUAURA</t>
+          <t>UGEL 09 HUAURA</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>VEGUETA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
-        <is>
-          <t>MAZO</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>150812</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>DRE LIMA PROVINCIAS</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>UGEL 09 HUAURA</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
@@ -12550,54 +10298,32 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>NUEVO PROGRESO</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>160510</t>
+        </is>
+      </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>DRE LORETO</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>REQUENA</t>
+          <t>UGEL REQUENA</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>JENARO HERRERA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
-        <is>
-          <t>NUEVO PROGRESO</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>160510</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>DRE LORETO</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>UGEL REQUENA</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Jenaro Herrera</t>
         </is>
@@ -12663,54 +10389,32 @@
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SAN ANTONIO DEL ESTRECHO</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>160801</t>
+        </is>
+      </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>DRE LORETO</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>PUTUMAYO</t>
+          <t>UGEL PUTUMAYO</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>PUTUMAYO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
-        <is>
-          <t>SAN ANTONIO DEL ESTRECHO</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>160801</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>DRE LORETO</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>UGEL PUTUMAYO</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>166 MARIA ANGELICA SOUSA MANIHUARI</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Putumayo</t>
         </is>
@@ -12776,54 +10480,32 @@
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SAN ANTONIO DEL ESTRECHO</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>160801</t>
+        </is>
+      </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>DRE LORETO</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>PUTUMAYO</t>
+          <t>UGEL PUTUMAYO</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>PUTUMAYO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
-        <is>
-          <t>SAN ANTONIO DEL ESTRECHO</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>160801</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>DRE LORETO</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>UGEL PUTUMAYO</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Putumayo</t>
         </is>
@@ -12895,54 +10577,32 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>200802</t>
+        </is>
+      </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>SECHURA</t>
+          <t>UGEL SECHURA</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>BELLAVISTA DE LA UNION</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>200802</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>DRE PIURA</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>UGEL SECHURA</t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG106" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Bellavista de la Union</t>
         </is>
@@ -13006,54 +10666,32 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>NUEVO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>200104</t>
+        </is>
+      </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>DRE PIURA</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>UGEL PIURA</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>CASTILLA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
-        <is>
-          <t>NUEVO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>200104</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>DRE PIURA</t>
-        </is>
-      </c>
-      <c r="AD107" t="inlineStr">
-        <is>
-          <t>UGEL PIURA</t>
-        </is>
-      </c>
-      <c r="AE107" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG107" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
@@ -13133,54 +10771,32 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SEGUNDA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
-        <is>
-          <t>SEGUNDA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -13260,54 +10876,32 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
-        <is>
-          <t>SAN PEDRO</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>00910</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -13387,54 +10981,32 @@
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SEGUNDA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
-        <is>
-          <t>SEGUNDA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>00849</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -13514,54 +11086,32 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>LA VICTORIA</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD111" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE111" t="inlineStr">
-        <is>
-          <t>00828/00828</t>
-        </is>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG111" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -13639,54 +11189,32 @@
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>PUERTO BAGAZAN</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
-        <is>
-          <t>PUERTO BAGAZAN</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>00821/00821</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -13766,54 +11294,32 @@
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SEGUNDA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
-        <is>
-          <t>SEGUNDA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD113" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>00123</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG113" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -13893,54 +11399,32 @@
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>NUEVA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
-        <is>
-          <t>NUEVA ESPERANZA</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>00875</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -14020,54 +11504,32 @@
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
-        <is>
-          <t>SAN PEDRO</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>1283/1283</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG115" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -14147,54 +11609,32 @@
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SEGUNDA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
-        <is>
-          <t>SEGUNDA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>313 JEHOVA ES MI PASTOR</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -14266,54 +11706,32 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SEGUNDA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
-        <is>
-          <t>SEGUNDA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>DIVINO MAESTRO</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG117" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -14391,54 +11809,32 @@
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>VALLE GRANDE</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
-        <is>
-          <t>VALLE GRANDE</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>1348</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -14526,54 +11922,32 @@
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SEGUNDA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
-        <is>
-          <t>SEGUNDA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>317/317</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -14651,54 +12025,32 @@
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>NACIENTE DEL RIO NEGRO</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
-        <is>
-          <t>NACIENTE DEL RIO NEGRO</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>00170</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -14778,54 +12130,32 @@
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SEGUNDA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
-        <is>
-          <t>SEGUNDA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>EMAUS/EMAUS</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
@@ -14905,54 +12235,32 @@
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SEGUNDA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>220803</t>
+        </is>
+      </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>DRE SAN MARTIN</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>RIOJA</t>
+          <t>UGEL RIOJA</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>ELIAS SOPLIN VARGAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
-        <is>
-          <t>SEGUNDA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>220803</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>00623/00623</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Elias Soplin Vargas</t>
         </is>
